--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/MISSISSIPPI_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/MISSISSIPPI_2022.xlsx
@@ -2940,7 +2940,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C144">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C154">
